--- a/output/pdf_financials_xlsx/AUTO.xlsx
+++ b/output/pdf_financials_xlsx/AUTO.xlsx
@@ -431,6 +431,21 @@
   </sheetPr>
   <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUTO.xlsx
+++ b/output/pdf_financials_xlsx/AUTO.xlsx
@@ -815,22 +815,22 @@
         <v>1.836201</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.494824</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>2.180272</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>1.252678</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5.778829</v>
+        <v>9.797909000000001</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2.269769</v>
+        <v>2.274196</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.619677</v>
+        <v>0.657704</v>
       </c>
     </row>
     <row r="11">
@@ -858,10 +858,10 @@
         <v>-0.5649650000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.494824</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-2.180272</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-1.252678</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-2.265342</v>
+        <v>-2.269769</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.58165</v>
+        <v>-0.619677</v>
       </c>
     </row>
     <row r="12">
@@ -1878,25 +1878,25 @@
         <v>0.273594</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.114696</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.684681</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.716054</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.321162</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.299123</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.00634</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.507711</v>
       </c>
     </row>
     <row r="35">
@@ -1964,25 +1964,25 @@
         <v>0.273594</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.114696</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.714681</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.746054</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.351162</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.329123</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.031108</v>
+        <v>0.037448</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.01504</v>
+        <v>0.522751</v>
       </c>
     </row>
     <row r="37">
@@ -2480,25 +2480,25 @@
         <v>0.134509</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.149606</v>
+        <v>0.03491</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.801214</v>
+        <v>0.116533</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.878985</v>
+        <v>0.162931</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.4553</v>
+        <v>0.134138</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.389983</v>
+        <v>0.09086</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.075726</v>
+        <v>0.069386</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.565176</v>
+        <v>0.057465</v>
       </c>
     </row>
     <row r="49">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -25738,7 +25738,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUTO.xlsx
+++ b/output/pdf_financials_xlsx/AUTO.xlsx
@@ -3201,25 +3201,25 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.293564</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.828035</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.580426</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.489274</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.830971</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.520292</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.52391</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
@@ -3330,25 +3330,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.131565</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.185248</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.180304</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.277924</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.368944</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.139763</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.455738</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.017786</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.59555</v>
       </c>
     </row>
     <row r="111">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.001108</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
@@ -5457,22 +5457,22 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.023632</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.052731</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.088681</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.032596</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.015734</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.027904</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -14110,7 +14110,11 @@
           <t>Accretion (Note 8, 9, 10 and 11)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -16208,7 +16212,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -19750,7 +19758,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>-0.023632</v>
       </c>
